--- a/nseIndia/exportedData/LiveAnalysisVariationsLoosersData.xlsx
+++ b/nseIndia/exportedData/LiveAnalysisVariationsLoosersData.xlsx
@@ -506,7 +506,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>TATASTEEL</t>
+          <t>M&amp;M</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -515,28 +515,28 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>160.02</v>
+        <v>3271</v>
       </c>
       <c r="D2" t="n">
-        <v>160.6</v>
+        <v>3280</v>
       </c>
       <c r="E2" t="n">
-        <v>156.5</v>
+        <v>3187</v>
       </c>
       <c r="F2" t="n">
-        <v>157.3</v>
+        <v>3200</v>
       </c>
       <c r="G2" t="n">
-        <v>160.18</v>
+        <v>3295.3</v>
       </c>
       <c r="H2" t="n">
-        <v>-1.8</v>
+        <v>-2.89</v>
       </c>
       <c r="I2" t="n">
-        <v>19720128</v>
+        <v>3017625</v>
       </c>
       <c r="J2" t="n">
-        <v>31043.4254976</v>
+        <v>96971.6811375</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -545,22 +545,22 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>06-Jun-2025</t>
+          <t>04-Jul-2025</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Dividend - Rs 3.60 Per Share</t>
+          <t>Dividend - Rs 25.30 Per Share</t>
         </is>
       </c>
       <c r="N2" t="n">
-        <v>-1.8</v>
+        <v>-2.89</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ADANIPORTS</t>
+          <t>RELIANCE</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -569,28 +569,28 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1324.8</v>
+        <v>1381.1</v>
       </c>
       <c r="D3" t="n">
-        <v>1329</v>
+        <v>1403.5</v>
       </c>
       <c r="E3" t="n">
-        <v>1298</v>
+        <v>1350</v>
       </c>
       <c r="F3" t="n">
-        <v>1300.1</v>
+        <v>1356</v>
       </c>
       <c r="G3" t="n">
-        <v>1319.6</v>
+        <v>1385.9</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.48</v>
+        <v>-2.16</v>
       </c>
       <c r="I3" t="n">
-        <v>1373243</v>
+        <v>18758842</v>
       </c>
       <c r="J3" t="n">
-        <v>17915.1908537</v>
+        <v>257960.3398788</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -599,22 +599,22 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>13-Jun-2025</t>
+          <t>14-Aug-2025</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Dividend - Rs 7 Per Share</t>
+          <t>Dividend - Rs 5.5 Per Share</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>-1.48</v>
+        <v>-2.16</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>HINDALCO</t>
+          <t>INFY</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -623,28 +623,28 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>701</v>
+        <v>1501.9</v>
       </c>
       <c r="D4" t="n">
-        <v>702.35</v>
+        <v>1501.9</v>
       </c>
       <c r="E4" t="n">
-        <v>688</v>
+        <v>1467.7</v>
       </c>
       <c r="F4" t="n">
-        <v>692.05</v>
+        <v>1469</v>
       </c>
       <c r="G4" t="n">
-        <v>700.5</v>
+        <v>1500.1</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.21</v>
+        <v>-2.07</v>
       </c>
       <c r="I4" t="n">
-        <v>2416838</v>
+        <v>8169075</v>
       </c>
       <c r="J4" t="n">
-        <v>16745.7871344</v>
+        <v>120884.338035</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -653,22 +653,22 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>08-Aug-2025</t>
+          <t>30-May-2025</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Dividend - Rs 5 Per Share</t>
+          <t>Dividend - Rs 22 Per Share</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>-1.21</v>
+        <v>-2.07</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>BEL</t>
+          <t>APOLLOHOSP</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -677,28 +677,28 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>387.85</v>
+        <v>7670</v>
       </c>
       <c r="D5" t="n">
-        <v>388</v>
+        <v>7744</v>
       </c>
       <c r="E5" t="n">
-        <v>382.55</v>
+        <v>7586</v>
       </c>
       <c r="F5" t="n">
-        <v>383.3</v>
+        <v>7611</v>
       </c>
       <c r="G5" t="n">
-        <v>388.85</v>
+        <v>7728</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.2</v>
+        <v>-1.51</v>
       </c>
       <c r="I5" t="n">
-        <v>3524161</v>
+        <v>481590</v>
       </c>
       <c r="J5" t="n">
-        <v>13531.7209917</v>
+        <v>36771.46733699999</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -707,22 +707,22 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>14-Aug-2025</t>
+          <t>19-Aug-2025</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Dividend - Rs 0.90 Per Share</t>
+          <t>Dividend - Rs 10 Per Share</t>
         </is>
       </c>
       <c r="N5" t="n">
-        <v>-1.43</v>
+        <v>-1.51</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ULTRACEMCO</t>
+          <t>ADANIENT</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -731,28 +731,28 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>12413</v>
+        <v>2283</v>
       </c>
       <c r="D6" t="n">
-        <v>12428</v>
+        <v>2289.7</v>
       </c>
       <c r="E6" t="n">
-        <v>12247</v>
+        <v>2240</v>
       </c>
       <c r="F6" t="n">
-        <v>12254</v>
+        <v>2247.9</v>
       </c>
       <c r="G6" t="n">
-        <v>12401</v>
+        <v>2275.2</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.19</v>
+        <v>-1.2</v>
       </c>
       <c r="I6" t="n">
-        <v>58011</v>
+        <v>795699</v>
       </c>
       <c r="J6" t="n">
-        <v>7144.7855886</v>
+        <v>17964.6554628</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -761,22 +761,22 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>25-Jul-2025</t>
+          <t>13-Jun-2025</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Dividend - Rs 77.50 Per Sh</t>
+          <t>Dividend - Rs 1.30 Per Share</t>
         </is>
       </c>
       <c r="N6" t="n">
-        <v>-1.19</v>
+        <v>-1.2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>JIOFIN</t>
+          <t>TATAMOTORS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -785,28 +785,28 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>330.6</v>
+        <v>675.45</v>
       </c>
       <c r="D7" t="n">
-        <v>331.95</v>
+        <v>681.15</v>
       </c>
       <c r="E7" t="n">
-        <v>325.85</v>
+        <v>668</v>
       </c>
       <c r="F7" t="n">
-        <v>327.1</v>
+        <v>669.5</v>
       </c>
       <c r="G7" t="n">
-        <v>330.6</v>
+        <v>675.45</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.06</v>
+        <v>-0.88</v>
       </c>
       <c r="I7" t="n">
-        <v>4115460</v>
+        <v>8201917</v>
       </c>
       <c r="J7" t="n">
-        <v>13500.354984</v>
+        <v>55239.910995</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -815,22 +815,22 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>11-Aug-2025</t>
+          <t>04-Jun-2025</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Dividend - Re 0.50 Per Share</t>
+          <t>Dividend - Rs 6 Per Share</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>-1.06</v>
+        <v>-0.88</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>LT</t>
+          <t>NTPC</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -839,28 +839,28 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>3700</v>
+        <v>331</v>
       </c>
       <c r="D8" t="n">
-        <v>3708.5</v>
+        <v>331.5</v>
       </c>
       <c r="E8" t="n">
-        <v>3641.7</v>
+        <v>327</v>
       </c>
       <c r="F8" t="n">
-        <v>3655.2</v>
+        <v>328</v>
       </c>
       <c r="G8" t="n">
-        <v>3693.7</v>
+        <v>330.8</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.04</v>
+        <v>-0.85</v>
       </c>
       <c r="I8" t="n">
-        <v>378886</v>
+        <v>11813425</v>
       </c>
       <c r="J8" t="n">
-        <v>13896.0987132</v>
+        <v>38762.21011</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -869,22 +869,22 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>03-Jun-2025</t>
+          <t>31-Jan-2025</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Dividend - Rs 34 Per Share</t>
+          <t>Interim Dividend - Rs 2.50 Per Share</t>
         </is>
       </c>
       <c r="N8" t="n">
-        <v>-1.04</v>
+        <v>-0.85</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>HEROMOTOCO</t>
+          <t>JSWSTEEL</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -893,28 +893,28 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>4770</v>
+        <v>1032</v>
       </c>
       <c r="D9" t="n">
-        <v>4773.5</v>
+        <v>1038.3</v>
       </c>
       <c r="E9" t="n">
-        <v>4722.1</v>
+        <v>1022.3</v>
       </c>
       <c r="F9" t="n">
-        <v>4728</v>
+        <v>1027</v>
       </c>
       <c r="G9" t="n">
-        <v>4768.7</v>
+        <v>1035.8</v>
       </c>
       <c r="H9" t="n">
         <v>-0.85</v>
       </c>
       <c r="I9" t="n">
-        <v>145741</v>
+        <v>1062037</v>
       </c>
       <c r="J9" t="n">
-        <v>6916.5472298</v>
+        <v>10932.3964706</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -923,12 +923,12 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>24-Jul-2025</t>
+          <t>08-Jul-2025</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Dividend - Rs 65 Per Share</t>
+          <t>Dividend - Rs 2.80 Per Share</t>
         </is>
       </c>
       <c r="N9" t="n">
@@ -938,7 +938,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SHRIRAMFIN</t>
+          <t>INDUSINDBK</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -947,28 +947,28 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>614.3</v>
+        <v>743</v>
       </c>
       <c r="D10" t="n">
-        <v>622.9</v>
+        <v>750.35</v>
       </c>
       <c r="E10" t="n">
-        <v>611.5</v>
+        <v>738</v>
       </c>
       <c r="F10" t="n">
-        <v>614.7</v>
+        <v>740.9</v>
       </c>
       <c r="G10" t="n">
-        <v>619.25</v>
+        <v>746.6</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.73</v>
+        <v>-0.76</v>
       </c>
       <c r="I10" t="n">
-        <v>1828924</v>
+        <v>2538543</v>
       </c>
       <c r="J10" t="n">
-        <v>11256.8443276</v>
+        <v>18855.7896954</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -977,22 +977,22 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>11-Jul-2025</t>
+          <t>28-Jun-2024</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Dividend - Rs 3 Per Share</t>
+          <t>Dividend - Rs 16.50 Per Share</t>
         </is>
       </c>
       <c r="N10" t="n">
-        <v>-0.73</v>
+        <v>-0.76</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ONGC</t>
+          <t>NESTLEIND</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1001,28 +1001,28 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>238.51</v>
+        <v>1160.3</v>
       </c>
       <c r="D11" t="n">
-        <v>238.67</v>
+        <v>1184.4</v>
       </c>
       <c r="E11" t="n">
-        <v>234.43</v>
+        <v>1150</v>
       </c>
       <c r="F11" t="n">
-        <v>237</v>
+        <v>1154.2</v>
       </c>
       <c r="G11" t="n">
-        <v>238.67</v>
+        <v>1162.4</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.7</v>
+        <v>-0.71</v>
       </c>
       <c r="I11" t="n">
-        <v>3241620</v>
+        <v>1593255</v>
       </c>
       <c r="J11" t="n">
-        <v>7659.623898</v>
+        <v>18519.99612</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1031,22 +1031,22 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>07-Feb-2025</t>
+          <t>08-Aug-2025</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Interim Dividend - Rs 5 Per Share</t>
+          <t>Bonus 1:1</t>
         </is>
       </c>
       <c r="N11" t="n">
-        <v>-0.7</v>
+        <v>-0.71</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>NTPC</t>
+          <t>BAJAJ-AUTO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1055,28 +1055,28 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>339.95</v>
+        <v>8714</v>
       </c>
       <c r="D12" t="n">
-        <v>340.45</v>
+        <v>8730</v>
       </c>
       <c r="E12" t="n">
-        <v>336.3</v>
+        <v>8571.5</v>
       </c>
       <c r="F12" t="n">
-        <v>337.9</v>
+        <v>8632</v>
       </c>
       <c r="G12" t="n">
-        <v>339.95</v>
+        <v>8689.5</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.6</v>
+        <v>-0.66</v>
       </c>
       <c r="I12" t="n">
-        <v>1610654</v>
+        <v>344340</v>
       </c>
       <c r="J12" t="n">
-        <v>5434.6687268</v>
+        <v>29789.128872</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1085,22 +1085,22 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>31-Jan-2025</t>
+          <t>20-Jun-2025</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Interim Dividend - Rs 2.50 Per Share</t>
+          <t>Dividend - Rs 210 Per Share</t>
         </is>
       </c>
       <c r="N12" t="n">
-        <v>-0.6</v>
+        <v>-0.66</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>JSWSTEEL</t>
+          <t>TECHM</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1109,28 +1109,28 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1055</v>
+        <v>1498.8</v>
       </c>
       <c r="D13" t="n">
-        <v>1058.1</v>
+        <v>1504.7</v>
       </c>
       <c r="E13" t="n">
-        <v>1045</v>
+        <v>1478.7</v>
       </c>
       <c r="F13" t="n">
-        <v>1047.5</v>
+        <v>1486</v>
       </c>
       <c r="G13" t="n">
-        <v>1053.7</v>
+        <v>1495.6</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.59</v>
+        <v>-0.64</v>
       </c>
       <c r="I13" t="n">
-        <v>263790</v>
+        <v>2279980</v>
       </c>
       <c r="J13" t="n">
-        <v>2764.387305</v>
+        <v>34106.448818</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1139,22 +1139,22 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>08-Jul-2025</t>
+          <t>04-Jul-2025</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Dividend - Rs 2.80 Per Share</t>
+          <t>Dividend - Rs 30 Per Share</t>
         </is>
       </c>
       <c r="N13" t="n">
-        <v>-0.59</v>
+        <v>-0.64</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>COALINDIA</t>
+          <t>SBILIFE</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1163,28 +1163,28 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>386.1</v>
+        <v>1826.9</v>
       </c>
       <c r="D14" t="n">
-        <v>386.85</v>
+        <v>1826.9</v>
       </c>
       <c r="E14" t="n">
-        <v>382.55</v>
+        <v>1801.1</v>
       </c>
       <c r="F14" t="n">
-        <v>383.95</v>
+        <v>1806.8</v>
       </c>
       <c r="G14" t="n">
-        <v>386.1</v>
+        <v>1816.8</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-0.55</v>
       </c>
       <c r="I14" t="n">
-        <v>879709</v>
+        <v>801378</v>
       </c>
       <c r="J14" t="n">
-        <v>3377.7306764</v>
+        <v>14491.9594764</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -1193,22 +1193,22 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>06-Aug-2025</t>
+          <t>07-Mar-2025</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Interim Dividend - Rs 5.50 Per Share</t>
+          <t>Interim Dividend - Rs 2.70 Per Share</t>
         </is>
       </c>
       <c r="N14" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-0.55</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>NESTLEIND</t>
+          <t>WIPRO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1217,28 +1217,28 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1099.9</v>
+        <v>250.5</v>
       </c>
       <c r="D15" t="n">
-        <v>1103</v>
+        <v>253.1</v>
       </c>
       <c r="E15" t="n">
-        <v>1092.2</v>
+        <v>248.66</v>
       </c>
       <c r="F15" t="n">
-        <v>1092.6</v>
+        <v>249.3</v>
       </c>
       <c r="G15" t="n">
-        <v>1096.9</v>
+        <v>250.65</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.39</v>
+        <v>-0.54</v>
       </c>
       <c r="I15" t="n">
-        <v>180106</v>
+        <v>10117017</v>
       </c>
       <c r="J15" t="n">
-        <v>1975.0784172</v>
+        <v>25354.2563037</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -1247,22 +1247,22 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>08-Aug-2025</t>
+          <t>28-Jul-2025</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Bonus 1:1</t>
+          <t>Interim Dividend - Rs 5 Per Share</t>
         </is>
       </c>
       <c r="N15" t="n">
-        <v>-0.39</v>
+        <v>-0.54</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>KOTAKBANK</t>
+          <t>EICHERMOT</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1271,28 +1271,28 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1988</v>
+        <v>6149</v>
       </c>
       <c r="D16" t="n">
-        <v>1993.5</v>
+        <v>6174.5</v>
       </c>
       <c r="E16" t="n">
-        <v>1975.5</v>
+        <v>6070</v>
       </c>
       <c r="F16" t="n">
-        <v>1980.1</v>
+        <v>6103</v>
       </c>
       <c r="G16" t="n">
-        <v>1987.7</v>
+        <v>6133</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.38</v>
+        <v>-0.49</v>
       </c>
       <c r="I16" t="n">
-        <v>1047131</v>
+        <v>496302</v>
       </c>
       <c r="J16" t="n">
-        <v>20795.2886683</v>
+        <v>30310.155744</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -1301,22 +1301,22 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>18-Jul-2025</t>
+          <t>01-Aug-2025</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Dividend - Rs 2.50 Per Share</t>
+          <t>Dividend - Rs 70 Per Share</t>
         </is>
       </c>
       <c r="N16" t="n">
-        <v>-0.38</v>
+        <v>-0.49</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ITC</t>
+          <t>TITAN</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1325,28 +1325,28 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>414.25</v>
+        <v>3637.7</v>
       </c>
       <c r="D17" t="n">
-        <v>415.05</v>
+        <v>3642</v>
       </c>
       <c r="E17" t="n">
-        <v>411.85</v>
+        <v>3603.6</v>
       </c>
       <c r="F17" t="n">
-        <v>412.6</v>
+        <v>3620.2</v>
       </c>
       <c r="G17" t="n">
-        <v>414.1</v>
+        <v>3637.7</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.36</v>
+        <v>-0.48</v>
       </c>
       <c r="I17" t="n">
-        <v>2999139</v>
+        <v>660956</v>
       </c>
       <c r="J17" t="n">
-        <v>12395.1415731</v>
+        <v>23932.555804</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -1355,22 +1355,22 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>28-May-2025</t>
+          <t>08-Jul-2025</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Dividend - Rs 7.85 Per Share</t>
+          <t>Dividend - Rs 11 Per Share</t>
         </is>
       </c>
       <c r="N17" t="n">
-        <v>-0.36</v>
+        <v>-0.48</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>BAJAJ-AUTO</t>
+          <t>HDFCBANK</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1379,28 +1379,28 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>8250</v>
+        <v>954</v>
       </c>
       <c r="D18" t="n">
-        <v>8280</v>
+        <v>963.3</v>
       </c>
       <c r="E18" t="n">
-        <v>8198</v>
+        <v>950.1</v>
       </c>
       <c r="F18" t="n">
-        <v>8220</v>
+        <v>953.4</v>
       </c>
       <c r="G18" t="n">
-        <v>8248.5</v>
+        <v>957.8</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.35</v>
+        <v>-0.46</v>
       </c>
       <c r="I18" t="n">
-        <v>104867</v>
+        <v>14823813</v>
       </c>
       <c r="J18" t="n">
-        <v>8621.776732100001</v>
+        <v>141602.9913012</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -1409,22 +1409,22 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>20-Jun-2025</t>
+          <t>26-Aug-2025</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Dividend - Rs 210 Per Share</t>
+          <t>Bonus 1:1</t>
         </is>
       </c>
       <c r="N18" t="n">
-        <v>-0.35</v>
+        <v>-0.46</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>SBILIFE</t>
+          <t>DRREDDY</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1433,28 +1433,28 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1842.1</v>
+        <v>1259</v>
       </c>
       <c r="D19" t="n">
-        <v>1853.7</v>
+        <v>1266.4</v>
       </c>
       <c r="E19" t="n">
-        <v>1832.2</v>
+        <v>1240.8</v>
       </c>
       <c r="F19" t="n">
-        <v>1834.3</v>
+        <v>1255.6</v>
       </c>
       <c r="G19" t="n">
-        <v>1840.3</v>
+        <v>1259.8</v>
       </c>
       <c r="H19" t="n">
         <v>-0.33</v>
       </c>
       <c r="I19" t="n">
-        <v>196952</v>
+        <v>2422956</v>
       </c>
       <c r="J19" t="n">
-        <v>3630.2980448</v>
+        <v>30481.2710712</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -1463,12 +1463,12 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>07-Mar-2025</t>
+          <t>10-Jul-2025</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Interim Dividend - Rs 2.70 Per Share</t>
+          <t>Dividend - Rs 8 Per Share</t>
         </is>
       </c>
       <c r="N19" t="n">
@@ -1478,7 +1478,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M&amp;M</t>
+          <t>TCS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1487,28 +1487,28 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>3273.2</v>
+        <v>3093</v>
       </c>
       <c r="D20" t="n">
-        <v>3313.5</v>
+        <v>3115</v>
       </c>
       <c r="E20" t="n">
-        <v>3267.3</v>
+        <v>3077.2</v>
       </c>
       <c r="F20" t="n">
-        <v>3274.3</v>
+        <v>3083.8</v>
       </c>
       <c r="G20" t="n">
-        <v>3282.2</v>
+        <v>3093.7</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.24</v>
+        <v>-0.32</v>
       </c>
       <c r="I20" t="n">
-        <v>655603</v>
+        <v>2271789</v>
       </c>
       <c r="J20" t="n">
-        <v>21513.9402465</v>
+        <v>70285.9711554</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -1517,16 +1517,16 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>04-Jul-2025</t>
+          <t>16-Jul-2025</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Dividend - Rs 25.30 Per Share</t>
+          <t>Interim Dividend - Rs 11 Per Share</t>
         </is>
       </c>
       <c r="N20" t="n">
-        <v>-0.24</v>
+        <v>-0.32</v>
       </c>
     </row>
     <row r="21">
@@ -1541,28 +1541,28 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1067</v>
+        <v>1052.1</v>
       </c>
       <c r="D21" t="n">
-        <v>1070.7</v>
+        <v>1063</v>
       </c>
       <c r="E21" t="n">
-        <v>1062</v>
+        <v>1042.5</v>
       </c>
       <c r="F21" t="n">
-        <v>1063.6</v>
+        <v>1048.9</v>
       </c>
       <c r="G21" t="n">
-        <v>1066</v>
+        <v>1051.9</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.23</v>
+        <v>-0.29</v>
       </c>
       <c r="I21" t="n">
-        <v>3552406</v>
+        <v>4718016</v>
       </c>
       <c r="J21" t="n">
-        <v>37939.3408394</v>
+        <v>49599.0868032</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -1580,7 +1580,7 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>-0.23</v>
+        <v>-0.29</v>
       </c>
     </row>
   </sheetData>
@@ -1594,7 +1594,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N7"/>
+  <dimension ref="A1:N9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1672,7 +1672,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>INDUSINDBK</t>
+          <t>BANKBARODA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1681,28 +1681,28 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>773.45</v>
+        <v>232.5</v>
       </c>
       <c r="D2" t="n">
-        <v>779.8</v>
+        <v>234.47</v>
       </c>
       <c r="E2" t="n">
-        <v>770.65</v>
+        <v>230.81</v>
       </c>
       <c r="F2" t="n">
-        <v>772.05</v>
+        <v>232.83</v>
       </c>
       <c r="G2" t="n">
-        <v>773.45</v>
+        <v>233.24</v>
       </c>
       <c r="H2" t="n">
         <v>-0.18</v>
       </c>
       <c r="I2" t="n">
-        <v>831445</v>
+        <v>5698267</v>
       </c>
       <c r="J2" t="n">
-        <v>6447.939119500001</v>
+        <v>13271.8336697</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -1711,12 +1711,12 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>28-Jun-2024</t>
+          <t>06-Jun-2025</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Dividend - Rs 16.50 Per Share</t>
+          <t>Dividend - Rs 8.35 Per Share</t>
         </is>
       </c>
       <c r="N2" t="n">
@@ -1726,7 +1726,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AXISBANK</t>
+          <t>ICICIBANK</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1735,28 +1735,28 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1067</v>
+        <v>1392.1</v>
       </c>
       <c r="D3" t="n">
-        <v>1070.7</v>
+        <v>1405</v>
       </c>
       <c r="E3" t="n">
-        <v>1062</v>
+        <v>1392.1</v>
       </c>
       <c r="F3" t="n">
-        <v>1063.6</v>
+        <v>1396.2</v>
       </c>
       <c r="G3" t="n">
-        <v>1066</v>
+        <v>1399.1</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.23</v>
+        <v>-0.21</v>
       </c>
       <c r="I3" t="n">
-        <v>3552406</v>
+        <v>8519507</v>
       </c>
       <c r="J3" t="n">
-        <v>37939.3408394</v>
+        <v>119256.9109367</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -1765,22 +1765,22 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>04-Jul-2025</t>
+          <t>12-Aug-2025</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Dividend - Re 1 Per Sh</t>
+          <t>Dividend - Rs 11 Per Share</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>-0.23</v>
+        <v>-0.21</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>AXISBANK</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1789,28 +1789,28 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>106.65</v>
+        <v>1052.1</v>
       </c>
       <c r="D4" t="n">
-        <v>107.15</v>
+        <v>1063</v>
       </c>
       <c r="E4" t="n">
-        <v>106.01</v>
+        <v>1042.5</v>
       </c>
       <c r="F4" t="n">
-        <v>106.33</v>
+        <v>1048.9</v>
       </c>
       <c r="G4" t="n">
-        <v>106.64</v>
+        <v>1051.9</v>
       </c>
       <c r="H4" t="n">
         <v>-0.29</v>
       </c>
       <c r="I4" t="n">
-        <v>3416024</v>
+        <v>4718016</v>
       </c>
       <c r="J4" t="n">
-        <v>3638.4071624</v>
+        <v>49599.0868032</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -1819,12 +1819,12 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>20-Jun-2025</t>
+          <t>04-Jul-2025</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Dividend - Rs 2.90 Per Share</t>
+          <t>Dividend - Re 1 Per Sh</t>
         </is>
       </c>
       <c r="N4" t="n">
@@ -1834,7 +1834,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>FEDERALBNK</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1843,28 +1843,28 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>196.39</v>
+        <v>101.01</v>
       </c>
       <c r="D5" t="n">
-        <v>196.68</v>
+        <v>102.42</v>
       </c>
       <c r="E5" t="n">
-        <v>195.45</v>
+        <v>100.6</v>
       </c>
       <c r="F5" t="n">
-        <v>195.55</v>
+        <v>101.05</v>
       </c>
       <c r="G5" t="n">
-        <v>196.19</v>
+        <v>101.45</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.33</v>
+        <v>-0.39</v>
       </c>
       <c r="I5" t="n">
-        <v>1041017</v>
+        <v>15792366</v>
       </c>
       <c r="J5" t="n">
-        <v>2039.9769132</v>
+        <v>15992.9290482</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -1873,22 +1873,22 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>23-Aug-2024</t>
+          <t>20-Jun-2025</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Annual General Meeting/Dividend - Rs 1.20 Per Share</t>
+          <t>Dividend - Rs 2.90 Per Share</t>
         </is>
       </c>
       <c r="N5" t="n">
-        <v>-0.33</v>
+        <v>-0.39</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>KOTAKBANK</t>
+          <t>HDFCBANK</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1897,28 +1897,28 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1988</v>
+        <v>954</v>
       </c>
       <c r="D6" t="n">
-        <v>1993.5</v>
+        <v>963.3</v>
       </c>
       <c r="E6" t="n">
-        <v>1975.5</v>
+        <v>950.1</v>
       </c>
       <c r="F6" t="n">
-        <v>1980.1</v>
+        <v>953.4</v>
       </c>
       <c r="G6" t="n">
-        <v>1987.7</v>
+        <v>957.8</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.38</v>
+        <v>-0.46</v>
       </c>
       <c r="I6" t="n">
-        <v>1047131</v>
+        <v>14823813</v>
       </c>
       <c r="J6" t="n">
-        <v>20795.2886683</v>
+        <v>141602.9913012</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -1927,22 +1927,22 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>18-Jul-2025</t>
+          <t>26-Aug-2025</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Dividend - Rs 2.50 Per Share</t>
+          <t>Bonus 1:1</t>
         </is>
       </c>
       <c r="N6" t="n">
-        <v>-0.38</v>
+        <v>-0.46</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>IDFCFIRSTB</t>
+          <t>CANBK</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1951,28 +1951,28 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>69.90000000000001</v>
+        <v>104.44</v>
       </c>
       <c r="D7" t="n">
-        <v>70</v>
+        <v>105.18</v>
       </c>
       <c r="E7" t="n">
-        <v>68.8</v>
+        <v>103.55</v>
       </c>
       <c r="F7" t="n">
-        <v>68.84999999999999</v>
+        <v>103.85</v>
       </c>
       <c r="G7" t="n">
-        <v>69.90000000000001</v>
+        <v>104.63</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.5</v>
+        <v>-0.75</v>
       </c>
       <c r="I7" t="n">
-        <v>6048750</v>
+        <v>13999620</v>
       </c>
       <c r="J7" t="n">
-        <v>4191.178875</v>
+        <v>14597.403774</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -1981,16 +1981,124 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>11-Jul-2025</t>
+          <t>13-Jun-2025</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Dividend - Rs 0.25 Per Share</t>
+          <t>Dividend - Rs 4 Per Share</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>-1.5</v>
+        <v>-0.75</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>INDUSINDBK</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>EQ</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>743</v>
+      </c>
+      <c r="D8" t="n">
+        <v>750.35</v>
+      </c>
+      <c r="E8" t="n">
+        <v>738</v>
+      </c>
+      <c r="F8" t="n">
+        <v>740.9</v>
+      </c>
+      <c r="G8" t="n">
+        <v>746.6</v>
+      </c>
+      <c r="H8" t="n">
+        <v>-0.76</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2538543</v>
+      </c>
+      <c r="J8" t="n">
+        <v>18855.7896954</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>28-Jun-2024</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Dividend - Rs 16.50 Per Share</t>
+        </is>
+      </c>
+      <c r="N8" t="n">
+        <v>-0.76</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>AUBANK</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>EQ</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>726</v>
+      </c>
+      <c r="D9" t="n">
+        <v>731.9</v>
+      </c>
+      <c r="E9" t="n">
+        <v>716.3</v>
+      </c>
+      <c r="F9" t="n">
+        <v>718.35</v>
+      </c>
+      <c r="G9" t="n">
+        <v>729.25</v>
+      </c>
+      <c r="H9" t="n">
+        <v>-1.49</v>
+      </c>
+      <c r="I9" t="n">
+        <v>3090760</v>
+      </c>
+      <c r="J9" t="n">
+        <v>22323.323176</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>04-Jul-2025</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Dividend - Re 1 Per Share</t>
+        </is>
+      </c>
+      <c r="N9" t="n">
+        <v>-1.49</v>
       </c>
     </row>
   </sheetData>
@@ -2082,7 +2190,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>JINDALSTEL</t>
+          <t>SWIGGY</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -2091,28 +2199,28 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>999.05</v>
+        <v>425</v>
       </c>
       <c r="D2" t="n">
-        <v>999.45</v>
+        <v>425</v>
       </c>
       <c r="E2" t="n">
-        <v>968.2</v>
+        <v>406.15</v>
       </c>
       <c r="F2" t="n">
-        <v>971.15</v>
+        <v>409.5</v>
       </c>
       <c r="G2" t="n">
-        <v>996.35</v>
+        <v>421</v>
       </c>
       <c r="H2" t="n">
-        <v>-2.53</v>
+        <v>-2.73</v>
       </c>
       <c r="I2" t="n">
-        <v>950337</v>
+        <v>13267998</v>
       </c>
       <c r="J2" t="n">
-        <v>9301.803522300001</v>
+        <v>54621.6941664</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -2121,22 +2229,22 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>22-Aug-2024</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Dividend - Rs 2 Per Share</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N2" t="n">
-        <v>-2.53</v>
+        <v>-2.73</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>VEDL</t>
+          <t>VBL</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -2145,28 +2253,28 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>439.4</v>
+        <v>495.1</v>
       </c>
       <c r="D3" t="n">
-        <v>439.7</v>
+        <v>499.4</v>
       </c>
       <c r="E3" t="n">
-        <v>428.2</v>
+        <v>483.9</v>
       </c>
       <c r="F3" t="n">
-        <v>430</v>
+        <v>485.95</v>
       </c>
       <c r="G3" t="n">
-        <v>438.75</v>
+        <v>497.7</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.99</v>
+        <v>-2.36</v>
       </c>
       <c r="I3" t="n">
-        <v>2630105</v>
+        <v>7064960</v>
       </c>
       <c r="J3" t="n">
-        <v>11340.486739</v>
+        <v>26923.6072646</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -2175,22 +2283,22 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>24-Jun-2025</t>
+          <t>01-Aug-2025</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Interim Dividend - Rs 7 Per Share</t>
+          <t>Interim Dividend - Re 0.50 Per Share</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>-1.99</v>
+        <v>-2.36</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>VBL</t>
+          <t>NAUKRI</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -2199,28 +2307,28 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>510.85</v>
+        <v>1390</v>
       </c>
       <c r="D4" t="n">
-        <v>510.85</v>
+        <v>1395</v>
       </c>
       <c r="E4" t="n">
-        <v>499.45</v>
+        <v>1354.5</v>
       </c>
       <c r="F4" t="n">
-        <v>504.55</v>
+        <v>1356.5</v>
       </c>
       <c r="G4" t="n">
-        <v>511.1</v>
+        <v>1386</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.28</v>
+        <v>-2.13</v>
       </c>
       <c r="I4" t="n">
-        <v>3135548</v>
+        <v>1215734</v>
       </c>
       <c r="J4" t="n">
-        <v>15737.6289668</v>
+        <v>16622.4878352</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -2229,22 +2337,22 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>01-Aug-2025</t>
+          <t>25-Jul-2025</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Interim Dividend - Re 0.50 Per Share</t>
+          <t>Dividend - Rs 3.60 Per Share</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>-1.28</v>
+        <v>-2.13</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AMBUJACEM</t>
+          <t>INDIGO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2253,28 +2361,28 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>580.85</v>
+        <v>5715</v>
       </c>
       <c r="D5" t="n">
-        <v>584.5</v>
+        <v>5739</v>
       </c>
       <c r="E5" t="n">
-        <v>572.5</v>
+        <v>5610</v>
       </c>
       <c r="F5" t="n">
-        <v>573.6</v>
+        <v>5615</v>
       </c>
       <c r="G5" t="n">
-        <v>580.85</v>
+        <v>5727</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.25</v>
+        <v>-1.96</v>
       </c>
       <c r="I5" t="n">
-        <v>968463</v>
+        <v>1628751</v>
       </c>
       <c r="J5" t="n">
-        <v>5583.2860413</v>
+        <v>92395.9496031</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -2283,22 +2391,22 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>13-Jun-2025</t>
+          <t>13-Aug-2025</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Dividend - Rs 2 Per Share</t>
+          <t>Dividend - Rs 10 Per Share</t>
         </is>
       </c>
       <c r="N5" t="n">
-        <v>-1.25</v>
+        <v>-1.96</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>MOTHERSON</t>
+          <t>JSWENERGY</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2307,28 +2415,28 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>93</v>
+        <v>498.05</v>
       </c>
       <c r="D6" t="n">
-        <v>93.89</v>
+        <v>498.85</v>
       </c>
       <c r="E6" t="n">
-        <v>91.62</v>
+        <v>485.5</v>
       </c>
       <c r="F6" t="n">
-        <v>92.26000000000001</v>
+        <v>487.95</v>
       </c>
       <c r="G6" t="n">
-        <v>93.39</v>
+        <v>497.65</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.21</v>
+        <v>-1.95</v>
       </c>
       <c r="I6" t="n">
-        <v>7194704</v>
+        <v>2020026</v>
       </c>
       <c r="J6" t="n">
-        <v>6647.187025599999</v>
+        <v>9931.457828999999</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -2337,22 +2445,22 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>18-Jul-2025</t>
+          <t>06-Jun-2025</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Bonus 1:2</t>
+          <t>Dividend - Rs 2 Per Share</t>
         </is>
       </c>
       <c r="N6" t="n">
-        <v>-1.21</v>
+        <v>-1.95</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>GODREJCP</t>
+          <t>LICI</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2361,28 +2469,28 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1197.5</v>
+        <v>868.9</v>
       </c>
       <c r="D7" t="n">
-        <v>1200.9</v>
+        <v>870.3</v>
       </c>
       <c r="E7" t="n">
-        <v>1182.7</v>
+        <v>850.1</v>
       </c>
       <c r="F7" t="n">
-        <v>1185.4</v>
+        <v>853.65</v>
       </c>
       <c r="G7" t="n">
-        <v>1198.8</v>
+        <v>869.5</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.12</v>
+        <v>-1.82</v>
       </c>
       <c r="I7" t="n">
-        <v>320259</v>
+        <v>926244</v>
       </c>
       <c r="J7" t="n">
-        <v>3817.9996944</v>
+        <v>7964.216409600001</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -2391,22 +2499,22 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>13-Aug-2025</t>
+          <t>25-Jul-2025</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Interim Dividend - Rs 5 Per Share</t>
+          <t>Dividend - Rs 12 Per Share</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>-1.12</v>
+        <v>-1.82</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ICICIGI</t>
+          <t>BAJAJHLDNG</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -2415,28 +2523,28 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1908</v>
+        <v>13030</v>
       </c>
       <c r="D8" t="n">
-        <v>1919.3</v>
+        <v>13040</v>
       </c>
       <c r="E8" t="n">
-        <v>1895.5</v>
+        <v>12751</v>
       </c>
       <c r="F8" t="n">
-        <v>1895.9</v>
+        <v>12751</v>
       </c>
       <c r="G8" t="n">
-        <v>1912.7</v>
+        <v>12966</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.88</v>
+        <v>-1.66</v>
       </c>
       <c r="I8" t="n">
-        <v>78565</v>
+        <v>38945</v>
       </c>
       <c r="J8" t="n">
-        <v>1499.271608</v>
+        <v>5012.112454</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -2445,22 +2553,22 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>06-Jun-2025</t>
+          <t>27-Jun-2025</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Dividend - Rs 7 Per Share</t>
+          <t>Dividend - Rs 28 Per Share</t>
         </is>
       </c>
       <c r="N8" t="n">
-        <v>-0.88</v>
+        <v>-1.66</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>JSWENERGY</t>
+          <t>JINDALSTEL</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2469,28 +2577,28 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>535</v>
+        <v>970.4</v>
       </c>
       <c r="D9" t="n">
-        <v>535.75</v>
+        <v>974.4</v>
       </c>
       <c r="E9" t="n">
-        <v>526.5</v>
+        <v>943.55</v>
       </c>
       <c r="F9" t="n">
-        <v>530.45</v>
+        <v>949.1</v>
       </c>
       <c r="G9" t="n">
-        <v>535</v>
+        <v>964.7</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.85</v>
+        <v>-1.62</v>
       </c>
       <c r="I9" t="n">
-        <v>531757</v>
+        <v>968556</v>
       </c>
       <c r="J9" t="n">
-        <v>2821.9280476</v>
+        <v>9232.082080800001</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -2499,7 +2607,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>06-Jun-2025</t>
+          <t>22-Aug-2025</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -2508,13 +2616,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>-0.85</v>
+        <v>-1.62</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>IOC</t>
+          <t>ICICIPRULI</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2523,28 +2631,28 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>143</v>
+        <v>612</v>
       </c>
       <c r="D10" t="n">
-        <v>143.16</v>
+        <v>612</v>
       </c>
       <c r="E10" t="n">
-        <v>140.75</v>
+        <v>598.5</v>
       </c>
       <c r="F10" t="n">
-        <v>141.24</v>
+        <v>599.95</v>
       </c>
       <c r="G10" t="n">
-        <v>142.43</v>
+        <v>609.55</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.84</v>
+        <v>-1.57</v>
       </c>
       <c r="I10" t="n">
-        <v>2908327</v>
+        <v>597806</v>
       </c>
       <c r="J10" t="n">
-        <v>4117.0277012</v>
+        <v>3598.493217</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -2553,22 +2661,22 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>08-Aug-2025</t>
+          <t>12-Jun-2025</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Dividend - Rs 3 Per Share</t>
+          <t>Dividend - Re 0.85 Per Share</t>
         </is>
       </c>
       <c r="N10" t="n">
-        <v>-0.84</v>
+        <v>-1.57</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BRITANNIA</t>
+          <t>RECLTD</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2577,28 +2685,28 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>5395</v>
+        <v>355.1</v>
       </c>
       <c r="D11" t="n">
-        <v>5398.5</v>
+        <v>355.8</v>
       </c>
       <c r="E11" t="n">
-        <v>5325</v>
+        <v>348.6</v>
       </c>
       <c r="F11" t="n">
-        <v>5333</v>
+        <v>349.95</v>
       </c>
       <c r="G11" t="n">
-        <v>5375.5</v>
+        <v>354.9</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.79</v>
+        <v>-1.39</v>
       </c>
       <c r="I11" t="n">
-        <v>65883</v>
+        <v>7976387</v>
       </c>
       <c r="J11" t="n">
-        <v>3524.7932064</v>
+        <v>28005.094757</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -2607,22 +2715,22 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>04-Aug-2025</t>
+          <t>14-Aug-2025</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Dividend - Rs 75 Per Share</t>
+          <t>Dividend - Rs 2.60 Per Share</t>
         </is>
       </c>
       <c r="N11" t="n">
-        <v>-0.79</v>
+        <v>-1.39</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>HAL</t>
+          <t>DLF</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2631,28 +2739,28 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>4537</v>
+        <v>747</v>
       </c>
       <c r="D12" t="n">
-        <v>4537</v>
+        <v>754.1</v>
       </c>
       <c r="E12" t="n">
-        <v>4472.4</v>
+        <v>737.55</v>
       </c>
       <c r="F12" t="n">
-        <v>4489.5</v>
+        <v>739.95</v>
       </c>
       <c r="G12" t="n">
-        <v>4524.4</v>
+        <v>749.45</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.77</v>
+        <v>-1.27</v>
       </c>
       <c r="I12" t="n">
-        <v>463056</v>
+        <v>3054170</v>
       </c>
       <c r="J12" t="n">
-        <v>20816.4972576</v>
+        <v>22746.541909</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -2661,22 +2769,22 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>18-Feb-2025</t>
+          <t>28-Jul-2025</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Interim Dividend - Rs 25 Per Share</t>
+          <t>Dividend - Rs 6 Per Share</t>
         </is>
       </c>
       <c r="N12" t="n">
-        <v>-0.77</v>
+        <v>-1.27</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>BPCL</t>
+          <t>SHREECEM</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2685,28 +2793,28 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>327</v>
+        <v>29795</v>
       </c>
       <c r="D13" t="n">
-        <v>331.4</v>
+        <v>29930</v>
       </c>
       <c r="E13" t="n">
-        <v>319</v>
+        <v>29210</v>
       </c>
       <c r="F13" t="n">
-        <v>320.05</v>
+        <v>29300</v>
       </c>
       <c r="G13" t="n">
-        <v>322.5</v>
+        <v>29675</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.76</v>
+        <v>-1.26</v>
       </c>
       <c r="I13" t="n">
-        <v>6491608</v>
+        <v>63260</v>
       </c>
       <c r="J13" t="n">
-        <v>20969.8413224</v>
+        <v>18649.26941</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -2715,22 +2823,22 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>31-Jul-2025</t>
+          <t>21-Jul-2025</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Dividend - Rs 5 Per Share</t>
+          <t>Dividend - Rs 60 Per Share</t>
         </is>
       </c>
       <c r="N13" t="n">
-        <v>-0.76</v>
+        <v>-1.26</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>DLF</t>
+          <t>IOC</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -2739,28 +2847,28 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>759</v>
+        <v>138.49</v>
       </c>
       <c r="D14" t="n">
-        <v>762.7</v>
+        <v>139.49</v>
       </c>
       <c r="E14" t="n">
-        <v>749.4</v>
+        <v>136.46</v>
       </c>
       <c r="F14" t="n">
-        <v>752.05</v>
+        <v>136.89</v>
       </c>
       <c r="G14" t="n">
-        <v>757.65</v>
+        <v>138.49</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.74</v>
+        <v>-1.16</v>
       </c>
       <c r="I14" t="n">
-        <v>675792</v>
+        <v>10577763</v>
       </c>
       <c r="J14" t="n">
-        <v>5101.3510704</v>
+        <v>14529.6152568</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -2769,22 +2877,22 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>28-Jul-2025</t>
+          <t>08-Aug-2025</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Dividend - Rs 6 Per Share</t>
+          <t>Dividend - Rs 3 Per Share</t>
         </is>
       </c>
       <c r="N14" t="n">
-        <v>-0.74</v>
+        <v>-1.16</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>IRFC</t>
+          <t>CHOLAFIN</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2793,28 +2901,28 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>125.65</v>
+        <v>1439</v>
       </c>
       <c r="D15" t="n">
-        <v>126.35</v>
+        <v>1452.3</v>
       </c>
       <c r="E15" t="n">
-        <v>124.61</v>
+        <v>1418</v>
       </c>
       <c r="F15" t="n">
-        <v>124.74</v>
+        <v>1423.7</v>
       </c>
       <c r="G15" t="n">
-        <v>125.65</v>
+        <v>1439.8</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.72</v>
+        <v>-1.12</v>
       </c>
       <c r="I15" t="n">
-        <v>2445564</v>
+        <v>1114003</v>
       </c>
       <c r="J15" t="n">
-        <v>3064.0471356</v>
+        <v>12478.7200496</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -2823,22 +2931,22 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>21-Mar-2025</t>
+          <t>24-Jul-2025</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Interim Dividend - Re 0.80 Per Share</t>
+          <t>Dividend - Re 0.70 Per Share</t>
         </is>
       </c>
       <c r="N15" t="n">
-        <v>-0.72</v>
+        <v>-1.12</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>TATAPOWER</t>
+          <t>ICICIGI</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2847,28 +2955,28 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>387.2</v>
+        <v>1852</v>
       </c>
       <c r="D16" t="n">
-        <v>388.6</v>
+        <v>1868.3</v>
       </c>
       <c r="E16" t="n">
-        <v>383.15</v>
+        <v>1832.1</v>
       </c>
       <c r="F16" t="n">
-        <v>384.65</v>
+        <v>1843</v>
       </c>
       <c r="G16" t="n">
-        <v>387.2</v>
+        <v>1860.3</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.66</v>
+        <v>-0.93</v>
       </c>
       <c r="I16" t="n">
-        <v>1011547</v>
+        <v>441249</v>
       </c>
       <c r="J16" t="n">
-        <v>3896.8836628</v>
+        <v>8146.780287</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -2877,22 +2985,22 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>20-Jun-2025</t>
+          <t>06-Jun-2025</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Dividend - Rs 2.25 Per Share</t>
+          <t>Dividend - Rs 7 Per Share</t>
         </is>
       </c>
       <c r="N16" t="n">
-        <v>-0.66</v>
+        <v>-0.93</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>ADANIENSOL</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2901,28 +3009,28 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>5100</v>
+        <v>775.4</v>
       </c>
       <c r="D17" t="n">
-        <v>5105.5</v>
+        <v>776.4</v>
       </c>
       <c r="E17" t="n">
-        <v>5043</v>
+        <v>759.25</v>
       </c>
       <c r="F17" t="n">
-        <v>5058</v>
+        <v>764</v>
       </c>
       <c r="G17" t="n">
-        <v>5087</v>
+        <v>770.95</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.57</v>
+        <v>-0.9</v>
       </c>
       <c r="I17" t="n">
-        <v>136625</v>
+        <v>1341814</v>
       </c>
       <c r="J17" t="n">
-        <v>6919.18185</v>
+        <v>10281.5155936</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -2931,22 +3039,22 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>08-Aug-2025</t>
+          <t>14-Jun-2024</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Interim Dividend - Rs 9.77 Per Share</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
       <c r="N17" t="n">
-        <v>-0.57</v>
+        <v>-0.9</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>HYUNDAI</t>
+          <t>VEDL</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2955,28 +3063,28 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>2244.9</v>
+        <v>424.5</v>
       </c>
       <c r="D18" t="n">
-        <v>2270</v>
+        <v>428.55</v>
       </c>
       <c r="E18" t="n">
-        <v>2225.8</v>
+        <v>420</v>
       </c>
       <c r="F18" t="n">
-        <v>2235</v>
+        <v>420.9</v>
       </c>
       <c r="G18" t="n">
-        <v>2246.7</v>
+        <v>424.5</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.52</v>
+        <v>-0.85</v>
       </c>
       <c r="I18" t="n">
-        <v>195599</v>
+        <v>7712901</v>
       </c>
       <c r="J18" t="n">
-        <v>4387.3638096</v>
+        <v>32657.1941241</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -2985,22 +3093,22 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>05-Aug-2025</t>
+          <t>26-Aug-2025</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Dividend - Rs 21 Per Share</t>
+          <t>Interim Dividend - Rs 16 Per Share</t>
         </is>
       </c>
       <c r="N18" t="n">
-        <v>-0.52</v>
+        <v>-0.85</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>DABUR</t>
+          <t>LODHA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -3009,28 +3117,28 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>504</v>
+        <v>1200</v>
       </c>
       <c r="D19" t="n">
-        <v>505.5</v>
+        <v>1216.2</v>
       </c>
       <c r="E19" t="n">
-        <v>500</v>
+        <v>1182.6</v>
       </c>
       <c r="F19" t="n">
-        <v>500.9</v>
+        <v>1199</v>
       </c>
       <c r="G19" t="n">
-        <v>503.5</v>
+        <v>1208.2</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.52</v>
+        <v>-0.76</v>
       </c>
       <c r="I19" t="n">
-        <v>349642</v>
+        <v>1005139</v>
       </c>
       <c r="J19" t="n">
-        <v>1756.9160858</v>
+        <v>12042.3693312</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -3039,22 +3147,22 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>18-Jul-2025</t>
+          <t>22-Aug-2025</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Dividend - Rs 5.25 Per Share</t>
+          <t>Dividend - Rs 4.25 Per Share</t>
         </is>
       </c>
       <c r="N19" t="n">
-        <v>-0.52</v>
+        <v>-0.76</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ADANIGREEN</t>
+          <t>CANBK</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -3063,28 +3171,28 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>925</v>
+        <v>104.44</v>
       </c>
       <c r="D20" t="n">
-        <v>933</v>
+        <v>105.18</v>
       </c>
       <c r="E20" t="n">
-        <v>917</v>
+        <v>103.55</v>
       </c>
       <c r="F20" t="n">
-        <v>919.45</v>
+        <v>103.85</v>
       </c>
       <c r="G20" t="n">
-        <v>924.15</v>
+        <v>104.63</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.51</v>
+        <v>-0.75</v>
       </c>
       <c r="I20" t="n">
-        <v>553952</v>
+        <v>13999620</v>
       </c>
       <c r="J20" t="n">
-        <v>5109.3208768</v>
+        <v>14597.403774</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -3093,22 +3201,22 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>14-Jun-2024</t>
+          <t>13-Jun-2025</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Dividend - Rs 4 Per Share</t>
         </is>
       </c>
       <c r="N20" t="n">
-        <v>-0.51</v>
+        <v>-0.75</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>CGPOWER</t>
+          <t>INDHOTEL</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -3117,28 +3225,28 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>676</v>
+        <v>766.85</v>
       </c>
       <c r="D21" t="n">
-        <v>676</v>
+        <v>776.7</v>
       </c>
       <c r="E21" t="n">
-        <v>666.3</v>
+        <v>757</v>
       </c>
       <c r="F21" t="n">
-        <v>667.6</v>
+        <v>759.75</v>
       </c>
       <c r="G21" t="n">
-        <v>670.45</v>
+        <v>765.15</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.43</v>
+        <v>-0.71</v>
       </c>
       <c r="I21" t="n">
-        <v>706503</v>
+        <v>3485485</v>
       </c>
       <c r="J21" t="n">
-        <v>4745.3687001</v>
+        <v>26714.4997825</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -3147,16 +3255,16 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>21-Mar-2025</t>
+          <t>30-Jun-2025</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Interim Dividend - Rs 1.30 Per Share</t>
+          <t>Dividend - Rs 2.25 Per Sh</t>
         </is>
       </c>
       <c r="N21" t="n">
-        <v>-0.43</v>
+        <v>-0.71</v>
       </c>
     </row>
   </sheetData>
@@ -3248,7 +3356,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>MAXHEALTH</t>
+          <t>BSE</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -3257,28 +3365,28 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1275</v>
+        <v>2180</v>
       </c>
       <c r="D2" t="n">
-        <v>1275</v>
+        <v>2184</v>
       </c>
       <c r="E2" t="n">
-        <v>1214.5</v>
+        <v>2090</v>
       </c>
       <c r="F2" t="n">
-        <v>1215.3</v>
+        <v>2099</v>
       </c>
       <c r="G2" t="n">
-        <v>1267.1</v>
+        <v>2178.4</v>
       </c>
       <c r="H2" t="n">
-        <v>-4.09</v>
+        <v>-3.64</v>
       </c>
       <c r="I2" t="n">
-        <v>2028661</v>
+        <v>8153679</v>
       </c>
       <c r="J2" t="n">
-        <v>24974.4398388</v>
+        <v>173364.3382659</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -3287,22 +3395,22 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>04-Jul-2025</t>
+          <t>23-May-2025</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Dividend - Rs 1.50 Per Share</t>
+          <t>Bonus 2:1</t>
         </is>
       </c>
       <c r="N2" t="n">
-        <v>-4.09</v>
+        <v>-3.64</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>NMDC</t>
+          <t>M&amp;M</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -3311,28 +3419,28 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>72.29000000000001</v>
+        <v>3271</v>
       </c>
       <c r="D3" t="n">
-        <v>72.29000000000001</v>
+        <v>3280</v>
       </c>
       <c r="E3" t="n">
-        <v>69</v>
+        <v>3187</v>
       </c>
       <c r="F3" t="n">
-        <v>69.34999999999999</v>
+        <v>3200</v>
       </c>
       <c r="G3" t="n">
-        <v>72.58</v>
+        <v>3295.3</v>
       </c>
       <c r="H3" t="n">
-        <v>-3.12</v>
+        <v>-2.89</v>
       </c>
       <c r="I3" t="n">
-        <v>21722664</v>
+        <v>3017625</v>
       </c>
       <c r="J3" t="n">
-        <v>15136.3522752</v>
+        <v>96971.6811375</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -3341,22 +3449,22 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>14-Aug-2025</t>
+          <t>04-Jul-2025</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Dividend - Re 1 Per Share</t>
+          <t>Dividend - Rs 25.30 Per Share</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>-4.45</v>
+        <v>-2.89</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>NHPC</t>
+          <t>NUVAMA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -3365,28 +3473,28 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>84.90000000000001</v>
+        <v>6576</v>
       </c>
       <c r="D4" t="n">
-        <v>84.98</v>
+        <v>6615</v>
       </c>
       <c r="E4" t="n">
-        <v>82</v>
+        <v>6371.5</v>
       </c>
       <c r="F4" t="n">
-        <v>82.33</v>
+        <v>6380.5</v>
       </c>
       <c r="G4" t="n">
-        <v>85.11</v>
+        <v>6549</v>
       </c>
       <c r="H4" t="n">
-        <v>-2.68</v>
+        <v>-2.57</v>
       </c>
       <c r="I4" t="n">
-        <v>4985008</v>
+        <v>129800</v>
       </c>
       <c r="J4" t="n">
-        <v>4142.0431472</v>
+        <v>8415.284460000001</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -3395,22 +3503,22 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>14-Aug-2025</t>
+          <t>03-Jun-2025</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Dividend - Rs 0.51 Per Share</t>
+          <t>Interim Dividend - Rs 69 Per Share</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>-3.27</v>
+        <v>-2.57</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>MCX</t>
+          <t>360ONE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -3419,28 +3527,28 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>8360</v>
+        <v>1037</v>
       </c>
       <c r="D5" t="n">
-        <v>8387.5</v>
+        <v>1045</v>
       </c>
       <c r="E5" t="n">
-        <v>8076</v>
+        <v>1013.3</v>
       </c>
       <c r="F5" t="n">
-        <v>8124</v>
+        <v>1018.1</v>
       </c>
       <c r="G5" t="n">
-        <v>8339</v>
+        <v>1043.9</v>
       </c>
       <c r="H5" t="n">
-        <v>-2.58</v>
+        <v>-2.47</v>
       </c>
       <c r="I5" t="n">
-        <v>282742</v>
+        <v>644147</v>
       </c>
       <c r="J5" t="n">
-        <v>23160.7261074</v>
+        <v>6613.1995902</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -3449,22 +3557,22 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>08-Aug-2025</t>
+          <t>29-Apr-2025</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Dividend - Rs 30 Per Share</t>
+          <t>Interim Dividend - Rs 6 Per Share</t>
         </is>
       </c>
       <c r="N5" t="n">
-        <v>-2.58</v>
+        <v>-2.47</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>JINDALSTEL</t>
+          <t>KFINTECH</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -3473,28 +3581,28 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>999.05</v>
+        <v>1042</v>
       </c>
       <c r="D6" t="n">
-        <v>999.45</v>
+        <v>1052.4</v>
       </c>
       <c r="E6" t="n">
-        <v>968.2</v>
+        <v>1018.7</v>
       </c>
       <c r="F6" t="n">
-        <v>971.15</v>
+        <v>1025</v>
       </c>
       <c r="G6" t="n">
-        <v>996.35</v>
+        <v>1050</v>
       </c>
       <c r="H6" t="n">
-        <v>-2.53</v>
+        <v>-2.38</v>
       </c>
       <c r="I6" t="n">
-        <v>950337</v>
+        <v>1097260</v>
       </c>
       <c r="J6" t="n">
-        <v>9301.803522300001</v>
+        <v>11338.865388</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -3503,22 +3611,22 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>22-Aug-2024</t>
+          <t>22-Aug-2025</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Dividend - Rs 2 Per Share</t>
+          <t>Dividend - Rs 7.50 Per Share</t>
         </is>
       </c>
       <c r="N6" t="n">
-        <v>-2.53</v>
+        <v>-2.38</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>IDEA</t>
+          <t>VBL</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3527,28 +3635,28 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>6.39</v>
+        <v>495.1</v>
       </c>
       <c r="D7" t="n">
-        <v>6.4</v>
+        <v>499.4</v>
       </c>
       <c r="E7" t="n">
-        <v>6.12</v>
+        <v>483.9</v>
       </c>
       <c r="F7" t="n">
-        <v>6.2</v>
+        <v>485.95</v>
       </c>
       <c r="G7" t="n">
-        <v>6.36</v>
+        <v>497.7</v>
       </c>
       <c r="H7" t="n">
-        <v>-2.52</v>
+        <v>-2.36</v>
       </c>
       <c r="I7" t="n">
-        <v>329372187</v>
+        <v>7064960</v>
       </c>
       <c r="J7" t="n">
-        <v>20585.7616875</v>
+        <v>26923.6072646</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -3557,22 +3665,22 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>20-Aug-2024</t>
+          <t>01-Aug-2025</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Interim Dividend - Re 0.50 Per Share</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>-2.52</v>
+        <v>-2.36</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>NBCC</t>
+          <t>ANGELONE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3581,28 +3689,28 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>105.75</v>
+        <v>2279.9</v>
       </c>
       <c r="D8" t="n">
-        <v>106.29</v>
+        <v>2297.5</v>
       </c>
       <c r="E8" t="n">
-        <v>103</v>
+        <v>2198.4</v>
       </c>
       <c r="F8" t="n">
-        <v>103.16</v>
+        <v>2209</v>
       </c>
       <c r="G8" t="n">
-        <v>105.78</v>
+        <v>2259.4</v>
       </c>
       <c r="H8" t="n">
-        <v>-2.48</v>
+        <v>-2.23</v>
       </c>
       <c r="I8" t="n">
-        <v>3677598</v>
+        <v>1577470</v>
       </c>
       <c r="J8" t="n">
-        <v>3832.7926356</v>
+        <v>35118.425875</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -3611,22 +3719,22 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>13-Aug-2025</t>
+          <t>30-May-2025</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Interim Dividend - Re 0.21 Per Share</t>
+          <t>Dividend - Rs 26 Per Share</t>
         </is>
       </c>
       <c r="N8" t="n">
-        <v>-2.48</v>
+        <v>-2.23</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>OIL</t>
+          <t>ASHOKLEY</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -3635,28 +3743,28 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>408.3</v>
+        <v>129.68</v>
       </c>
       <c r="D9" t="n">
-        <v>409.6</v>
+        <v>130.24</v>
       </c>
       <c r="E9" t="n">
-        <v>396.5</v>
+        <v>126.76</v>
       </c>
       <c r="F9" t="n">
-        <v>397.45</v>
+        <v>126.95</v>
       </c>
       <c r="G9" t="n">
-        <v>407</v>
+        <v>129.82</v>
       </c>
       <c r="H9" t="n">
-        <v>-2.35</v>
+        <v>-2.21</v>
       </c>
       <c r="I9" t="n">
-        <v>1729646</v>
+        <v>10674470</v>
       </c>
       <c r="J9" t="n">
-        <v>6930.172628200001</v>
+        <v>13683.603093</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -3665,22 +3773,22 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>17-Feb-2025</t>
+          <t>16-Jul-2025</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Interim Dividend - Rs 7 Per Share</t>
+          <t>Bonus 1:1</t>
         </is>
       </c>
       <c r="N9" t="n">
-        <v>-2.35</v>
+        <v>-2.21</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SAIL</t>
+          <t>RELIANCE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -3689,28 +3797,28 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>124.2</v>
+        <v>1381.1</v>
       </c>
       <c r="D10" t="n">
-        <v>124.35</v>
+        <v>1403.5</v>
       </c>
       <c r="E10" t="n">
-        <v>121.11</v>
+        <v>1350</v>
       </c>
       <c r="F10" t="n">
-        <v>121.24</v>
+        <v>1356</v>
       </c>
       <c r="G10" t="n">
-        <v>124.05</v>
+        <v>1385.9</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.27</v>
+        <v>-2.16</v>
       </c>
       <c r="I10" t="n">
-        <v>3343004</v>
+        <v>18758842</v>
       </c>
       <c r="J10" t="n">
-        <v>4078.7991804</v>
+        <v>257960.3398788</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -3719,22 +3827,22 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>19-Sep-2024</t>
+          <t>14-Aug-2025</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Dividend - Rs 5.5 Per Share</t>
         </is>
       </c>
       <c r="N10" t="n">
-        <v>-2.27</v>
+        <v>-2.16</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>VEDL</t>
+          <t>PAYTM</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -3743,28 +3851,28 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>439.4</v>
+        <v>1227</v>
       </c>
       <c r="D11" t="n">
-        <v>439.7</v>
+        <v>1234</v>
       </c>
       <c r="E11" t="n">
-        <v>428.2</v>
+        <v>1203.5</v>
       </c>
       <c r="F11" t="n">
-        <v>430</v>
+        <v>1204.2</v>
       </c>
       <c r="G11" t="n">
-        <v>438.75</v>
+        <v>1230.8</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.99</v>
+        <v>-2.16</v>
       </c>
       <c r="I11" t="n">
-        <v>2630105</v>
+        <v>3601954</v>
       </c>
       <c r="J11" t="n">
-        <v>11340.486739</v>
+        <v>43925.1086392</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -3773,22 +3881,22 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>24-Jun-2025</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Interim Dividend - Rs 7 Per Share</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N11" t="n">
-        <v>-1.99</v>
+        <v>-2.16</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>NUVAMA</t>
+          <t>NAUKRI</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -3797,28 +3905,28 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>6980</v>
+        <v>1390</v>
       </c>
       <c r="D12" t="n">
-        <v>7143.5</v>
+        <v>1395</v>
       </c>
       <c r="E12" t="n">
-        <v>6773.5</v>
+        <v>1354.5</v>
       </c>
       <c r="F12" t="n">
-        <v>6794</v>
+        <v>1356.5</v>
       </c>
       <c r="G12" t="n">
-        <v>6930</v>
+        <v>1386</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.96</v>
+        <v>-2.13</v>
       </c>
       <c r="I12" t="n">
-        <v>220657</v>
+        <v>1215734</v>
       </c>
       <c r="J12" t="n">
-        <v>15437.7815596</v>
+        <v>16622.4878352</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -3827,22 +3935,22 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>03-Jun-2025</t>
+          <t>25-Jul-2025</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Interim Dividend - Rs 69 Per Share</t>
+          <t>Dividend - Rs 3.60 Per Share</t>
         </is>
       </c>
       <c r="N12" t="n">
-        <v>-1.96</v>
+        <v>-2.13</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>TATASTEEL</t>
+          <t>IIFL</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -3851,28 +3959,28 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>160.02</v>
+        <v>436</v>
       </c>
       <c r="D13" t="n">
-        <v>160.6</v>
+        <v>440.45</v>
       </c>
       <c r="E13" t="n">
-        <v>156.5</v>
+        <v>425.9</v>
       </c>
       <c r="F13" t="n">
-        <v>157.3</v>
+        <v>427.1</v>
       </c>
       <c r="G13" t="n">
-        <v>160.18</v>
+        <v>436.2</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.8</v>
+        <v>-2.09</v>
       </c>
       <c r="I13" t="n">
-        <v>19720128</v>
+        <v>1027543</v>
       </c>
       <c r="J13" t="n">
-        <v>31043.4254976</v>
+        <v>4435.903131</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -3881,22 +3989,22 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>06-Jun-2025</t>
+          <t>23-Sep-2024</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Dividend - Rs 3.60 Per Share</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
       <c r="N13" t="n">
-        <v>-1.8</v>
+        <v>-2.09</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>IDFCFIRSTB</t>
+          <t>INFY</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3905,28 +4013,28 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>69.90000000000001</v>
+        <v>1501.9</v>
       </c>
       <c r="D14" t="n">
-        <v>70</v>
+        <v>1501.9</v>
       </c>
       <c r="E14" t="n">
-        <v>68.8</v>
+        <v>1467.7</v>
       </c>
       <c r="F14" t="n">
-        <v>68.84999999999999</v>
+        <v>1469</v>
       </c>
       <c r="G14" t="n">
-        <v>69.90000000000001</v>
+        <v>1500.1</v>
       </c>
       <c r="H14" t="n">
-        <v>-1.5</v>
+        <v>-2.07</v>
       </c>
       <c r="I14" t="n">
-        <v>6048750</v>
+        <v>8169075</v>
       </c>
       <c r="J14" t="n">
-        <v>4191.178875</v>
+        <v>120884.338035</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -3935,22 +4043,22 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>11-Jul-2025</t>
+          <t>30-May-2025</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Dividend - Rs 0.25 Per Share</t>
+          <t>Dividend - Rs 22 Per Share</t>
         </is>
       </c>
       <c r="N14" t="n">
-        <v>-1.5</v>
+        <v>-2.07</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>INDIGO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3959,28 +4067,28 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>189.94</v>
+        <v>5715</v>
       </c>
       <c r="D15" t="n">
-        <v>190.01</v>
+        <v>5739</v>
       </c>
       <c r="E15" t="n">
-        <v>186.25</v>
+        <v>5610</v>
       </c>
       <c r="F15" t="n">
-        <v>187.13</v>
+        <v>5615</v>
       </c>
       <c r="G15" t="n">
-        <v>189.94</v>
+        <v>5727</v>
       </c>
       <c r="H15" t="n">
-        <v>-1.48</v>
+        <v>-1.96</v>
       </c>
       <c r="I15" t="n">
-        <v>3732291</v>
+        <v>1628751</v>
       </c>
       <c r="J15" t="n">
-        <v>6998.045625</v>
+        <v>92395.9496031</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -3989,22 +4097,22 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>14-Feb-2025</t>
+          <t>13-Aug-2025</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Interim Dividend - Rs 4 Per Share</t>
+          <t>Dividend - Rs 10 Per Share</t>
         </is>
       </c>
       <c r="N15" t="n">
-        <v>-1.48</v>
+        <v>-1.96</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ADANIPORTS</t>
+          <t>JSWENERGY</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -4013,28 +4121,28 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1324.8</v>
+        <v>498.05</v>
       </c>
       <c r="D16" t="n">
-        <v>1329</v>
+        <v>498.85</v>
       </c>
       <c r="E16" t="n">
-        <v>1298</v>
+        <v>485.5</v>
       </c>
       <c r="F16" t="n">
-        <v>1300.1</v>
+        <v>487.95</v>
       </c>
       <c r="G16" t="n">
-        <v>1319.6</v>
+        <v>497.65</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.48</v>
+        <v>-1.95</v>
       </c>
       <c r="I16" t="n">
-        <v>1373243</v>
+        <v>2020026</v>
       </c>
       <c r="J16" t="n">
-        <v>17915.1908537</v>
+        <v>9931.457828999999</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -4043,22 +4151,22 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>13-Jun-2025</t>
+          <t>06-Jun-2025</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Dividend - Rs 7 Per Share</t>
+          <t>Dividend - Rs 2 Per Share</t>
         </is>
       </c>
       <c r="N16" t="n">
-        <v>-1.48</v>
+        <v>-1.95</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>INDUSTOWER</t>
+          <t>HDFCAMC</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -4067,28 +4175,28 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>337.2</v>
+        <v>5589.5</v>
       </c>
       <c r="D17" t="n">
-        <v>337.8</v>
+        <v>5618</v>
       </c>
       <c r="E17" t="n">
-        <v>330.2</v>
+        <v>5450</v>
       </c>
       <c r="F17" t="n">
-        <v>332.55</v>
+        <v>5475</v>
       </c>
       <c r="G17" t="n">
-        <v>337.3</v>
+        <v>5582</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.41</v>
+        <v>-1.92</v>
       </c>
       <c r="I17" t="n">
-        <v>3833600</v>
+        <v>464107</v>
       </c>
       <c r="J17" t="n">
-        <v>12770.10496</v>
+        <v>25607.3821892</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -4097,22 +4205,22 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>09-Aug-2024</t>
+          <t>06-Jun-2025</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Buy Back</t>
+          <t>Dividend - Rs 90 Per Share</t>
         </is>
       </c>
       <c r="N17" t="n">
-        <v>-1.41</v>
+        <v>-1.92</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>PRESTIGE</t>
+          <t>GODREJPROP</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -4121,28 +4229,28 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1630</v>
+        <v>1985</v>
       </c>
       <c r="D18" t="n">
-        <v>1639.9</v>
+        <v>1998</v>
       </c>
       <c r="E18" t="n">
-        <v>1602.6</v>
+        <v>1941</v>
       </c>
       <c r="F18" t="n">
-        <v>1606.7</v>
+        <v>1947</v>
       </c>
       <c r="G18" t="n">
-        <v>1628.9</v>
+        <v>1984.6</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.36</v>
+        <v>-1.89</v>
       </c>
       <c r="I18" t="n">
-        <v>148570</v>
+        <v>1246366</v>
       </c>
       <c r="J18" t="n">
-        <v>2396.092389</v>
+        <v>14104.4102485</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -4151,22 +4259,22 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>23-Sep-2024</t>
+          <t>27-Jul-2015</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Dividend - Rs 1.80 Per Share</t>
+          <t>Annual General Meeting/Dividend -  Rs 2/- Per Share</t>
         </is>
       </c>
       <c r="N18" t="n">
-        <v>-1.36</v>
+        <v>-1.89</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>CONCOR</t>
+          <t>TATAELXSI</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -4175,28 +4283,28 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>541.55</v>
+        <v>5338</v>
       </c>
       <c r="D19" t="n">
-        <v>542</v>
+        <v>5343</v>
       </c>
       <c r="E19" t="n">
-        <v>533.6</v>
+        <v>5221</v>
       </c>
       <c r="F19" t="n">
-        <v>534.3</v>
+        <v>5240</v>
       </c>
       <c r="G19" t="n">
-        <v>541.55</v>
+        <v>5338</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.34</v>
+        <v>-1.84</v>
       </c>
       <c r="I19" t="n">
-        <v>493013</v>
+        <v>201277</v>
       </c>
       <c r="J19" t="n">
-        <v>2645.6063606</v>
+        <v>10612.0681649</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -4205,22 +4313,22 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>13-Aug-2025</t>
+          <t>11-Jun-2025</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Interim Dividend - Rs 1.60 Per Share</t>
+          <t>Dividend - Rs 75 Per Share</t>
         </is>
       </c>
       <c r="N19" t="n">
-        <v>-1.34</v>
+        <v>-1.84</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>SJVN</t>
+          <t>TITAGARH</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -4229,28 +4337,28 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>93.90000000000001</v>
+        <v>841.5</v>
       </c>
       <c r="D20" t="n">
-        <v>94</v>
+        <v>851</v>
       </c>
       <c r="E20" t="n">
-        <v>92.05</v>
+        <v>823</v>
       </c>
       <c r="F20" t="n">
-        <v>92.22</v>
+        <v>825</v>
       </c>
       <c r="G20" t="n">
-        <v>93.45</v>
+        <v>840.35</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.32</v>
+        <v>-1.83</v>
       </c>
       <c r="I20" t="n">
-        <v>2576664</v>
+        <v>858040</v>
       </c>
       <c r="J20" t="n">
-        <v>2392.1748576</v>
+        <v>7175.960128</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -4259,22 +4367,22 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>21-Feb-2025</t>
+          <t>20-Aug-2024</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Interim Dividend - Rs 1.15 Per Share</t>
+          <t>Annual General Meeting/Dividend - Re 0.80 Per Share</t>
         </is>
       </c>
       <c r="N20" t="n">
-        <v>-1.32</v>
+        <v>-1.83</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>PATANJALI</t>
+          <t>RVNL</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -4283,28 +4391,28 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1806</v>
+        <v>308.4</v>
       </c>
       <c r="D21" t="n">
-        <v>1806</v>
+        <v>309</v>
       </c>
       <c r="E21" t="n">
-        <v>1769</v>
+        <v>301.75</v>
       </c>
       <c r="F21" t="n">
-        <v>1773.9</v>
+        <v>303</v>
       </c>
       <c r="G21" t="n">
-        <v>1797.5</v>
+        <v>308.65</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.31</v>
+        <v>-1.83</v>
       </c>
       <c r="I21" t="n">
-        <v>185390</v>
+        <v>4853561</v>
       </c>
       <c r="J21" t="n">
-        <v>3308.358706</v>
+        <v>14826.6581428</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -4313,16 +4421,16 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>04-Nov-2024</t>
+          <t>21-Aug-2025</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Interim Dividend - Rs 8 Per Share</t>
+          <t>Dividend - Rs 1.72 Per Share</t>
         </is>
       </c>
       <c r="N21" t="n">
-        <v>-1.31</v>
+        <v>-1.83</v>
       </c>
     </row>
   </sheetData>
